--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -430,7 +430,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -541,7 +541,7 @@
     <t>as-dp-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-practitioner|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dp-practitioner|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Practitioner.meta.security</t>
@@ -729,7 +729,7 @@
     <t>as-ext-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-registration|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1035,7 +1035,7 @@
     <t>as-ext-frpractitioner-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>as-ext-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-smartcard|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1311,7 +1311,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1960,7 +1960,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2042,7 +2042,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2310,7 +2310,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-1}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2552,7 +2552,7 @@
     <t>as-ext-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-education-level|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -2809,7 +2809,7 @@
     <t>Practitioner.qualification:degree.issuer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -3009,7 +3009,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-1}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
